--- a/results/log_pv_cap/log_pv_cap_densities_pdensity_tests.xlsx
+++ b/results/log_pv_cap/log_pv_cap_densities_pdensity_tests.xlsx
@@ -451,27 +451,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>80.67***</t>
+          <t>74.03***</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>39.55***</t>
+          <t>48.11***</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8072.46***</t>
+          <t>7795.02***</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>79.38***</t>
+          <t>71.67***</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>474.21***</t>
+          <t>405.90***</t>
         </is>
       </c>
     </row>
@@ -483,27 +483,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>80.67***</t>
+          <t>74.03***</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8.82***</t>
+          <t>10.69***</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6585.89***</t>
+          <t>5594.71***</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20.10***</t>
+          <t>18.37***</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>474.21***</t>
+          <t>405.90***</t>
         </is>
       </c>
     </row>
@@ -515,27 +515,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>80.67***</t>
+          <t>74.03***</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>8.68***</t>
+          <t>10.27***</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6583.45***</t>
+          <t>5585.81***</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>13.49***</t>
+          <t>12.49***</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>474.21***</t>
+          <t>405.90***</t>
         </is>
       </c>
     </row>
